--- a/templates/retail_cma/CMA_Retail.xlsx
+++ b/templates/retail_cma/CMA_Retail.xlsx
@@ -4085,23 +4085,23 @@
         </is>
       </c>
       <c r="C25" s="304">
-        <f>IFERROR(C16/AVERAGE(C14,C17),0)</f>
+        <f>IFERROR(C16/IF(C14=0,C17,AVERAGE(C14,C17)),0)</f>
         <v/>
       </c>
       <c r="D25" s="304">
-        <f>IFERROR(D16/AVERAGE(D14,D17),0)</f>
+        <f>IFERROR(D16/IF(D14=0,D17,AVERAGE(D14,D17)),0)</f>
         <v/>
       </c>
       <c r="E25" s="304">
-        <f>IFERROR(E16/AVERAGE(E14,E17),0)</f>
+        <f>IFERROR(E16/IF(E14=0,E17,AVERAGE(E14,E17)),0)</f>
         <v/>
       </c>
       <c r="F25" s="304">
-        <f>IFERROR(F16/AVERAGE(F14,F17),0)</f>
+        <f>IFERROR(F16/IF(F14=0,F17,AVERAGE(F14,F17)),0)</f>
         <v/>
       </c>
       <c r="G25" s="304">
-        <f>IFERROR(G16/AVERAGE(G14,G17),0)</f>
+        <f>IFERROR(G16/IF(G14=0,G17,AVERAGE(G14,G17)),0)</f>
         <v/>
       </c>
     </row>
